--- a/apps/deep/www/calculators/nc-sqt-adapted.xlsx
+++ b/apps/deep/www/calculators/nc-sqt-adapted.xlsx
@@ -1542,7 +1542,7 @@
     <row r="3" ht="21" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -1675,7 +1675,7 @@
     <row r="4" ht="21" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -2857,7 +2857,7 @@
     <row r="3" ht="21" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -6294,7 +6294,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -6338,7 +6338,7 @@
     <row r="3" ht="21" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -12314,7 +12314,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -12348,7 +12348,7 @@
     <row r="2" ht="21" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -12545,7 +12545,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -12978,7 +12978,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
